--- a/fmwww.bc.edu/repec/bocode/r/rollbook.xlsx
+++ b/fmwww.bc.edu/repec/bocode/r/rollbook.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16457" windowHeight="6497"/>
+    <workbookView windowWidth="16457" windowHeight="6651"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="169">
   <si>
     <t>序号</t>
   </si>
@@ -43,6 +43,216 @@
     <t>专业</t>
   </si>
   <si>
+    <t>任美婷</t>
+  </si>
+  <si>
+    <t>会计</t>
+  </si>
+  <si>
+    <t>童节</t>
+  </si>
+  <si>
+    <t>马穗源</t>
+  </si>
+  <si>
+    <t>钱高琪</t>
+  </si>
+  <si>
+    <t>洪豆豆</t>
+  </si>
+  <si>
+    <t>董赛</t>
+  </si>
+  <si>
+    <t>欧家秀</t>
+  </si>
+  <si>
+    <t>吴雨涵</t>
+  </si>
+  <si>
+    <t>何璐璐</t>
+  </si>
+  <si>
+    <t>查雨薇</t>
+  </si>
+  <si>
+    <t>陈彦彤</t>
+  </si>
+  <si>
+    <t>王紫阳</t>
+  </si>
+  <si>
+    <t>蒋礼馨</t>
+  </si>
+  <si>
+    <t>侯生遥</t>
+  </si>
+  <si>
+    <t>薛淑洁</t>
+  </si>
+  <si>
+    <t>徐心雨</t>
+  </si>
+  <si>
+    <t>鲍士城</t>
+  </si>
+  <si>
+    <t>刘晓漾</t>
+  </si>
+  <si>
+    <t>张伊美</t>
+  </si>
+  <si>
+    <t>刘婧</t>
+  </si>
+  <si>
+    <t>柴茉</t>
+  </si>
+  <si>
+    <t>杨玉琼</t>
+  </si>
+  <si>
+    <t>方彬</t>
+  </si>
+  <si>
+    <t>袁万明</t>
+  </si>
+  <si>
+    <t>姚子情</t>
+  </si>
+  <si>
+    <t>胡晓雨</t>
+  </si>
+  <si>
+    <t>于笑笑</t>
+  </si>
+  <si>
+    <t>何伟悦</t>
+  </si>
+  <si>
+    <t>张欣然</t>
+  </si>
+  <si>
+    <t>成方圆</t>
+  </si>
+  <si>
+    <t>查芳芳</t>
+  </si>
+  <si>
+    <t>胡瑾依</t>
+  </si>
+  <si>
+    <t>凌雪</t>
+  </si>
+  <si>
+    <t>张焱</t>
+  </si>
+  <si>
+    <t>陈燕</t>
+  </si>
+  <si>
+    <t>葛玲玉</t>
+  </si>
+  <si>
+    <t>马燕</t>
+  </si>
+  <si>
+    <t>朱月</t>
+  </si>
+  <si>
+    <t>陈蕊</t>
+  </si>
+  <si>
+    <t>徐友新</t>
+  </si>
+  <si>
+    <t>陈宏霞</t>
+  </si>
+  <si>
+    <t>侯骁娱</t>
+  </si>
+  <si>
+    <t>吉鸿帆</t>
+  </si>
+  <si>
+    <t>宋可欣</t>
+  </si>
+  <si>
+    <t>汪璇</t>
+  </si>
+  <si>
+    <t>尹梦琴</t>
+  </si>
+  <si>
+    <t>王洁</t>
+  </si>
+  <si>
+    <t>赵鸽遥</t>
+  </si>
+  <si>
+    <t>杨潍硕</t>
+  </si>
+  <si>
+    <t>任强文</t>
+  </si>
+  <si>
+    <t>杜威</t>
+  </si>
+  <si>
+    <t>吴嘉伟</t>
+  </si>
+  <si>
+    <t>韩仁婕</t>
+  </si>
+  <si>
+    <t>刘德重</t>
+  </si>
+  <si>
+    <t>黄嘉婕</t>
+  </si>
+  <si>
+    <t>刘宇萌</t>
+  </si>
+  <si>
+    <t>于晓航</t>
+  </si>
+  <si>
+    <t>罗其杰</t>
+  </si>
+  <si>
+    <t>黄金艳</t>
+  </si>
+  <si>
+    <t>刘莲姣</t>
+  </si>
+  <si>
+    <t>汪新悦</t>
+  </si>
+  <si>
+    <t>王展鹏</t>
+  </si>
+  <si>
+    <t>孙文静</t>
+  </si>
+  <si>
+    <t>昝雨洁</t>
+  </si>
+  <si>
+    <t>郑骏莉</t>
+  </si>
+  <si>
+    <t>汤雨蒙</t>
+  </si>
+  <si>
+    <t>苏新宇</t>
+  </si>
+  <si>
+    <t>朱娟娟</t>
+  </si>
+  <si>
+    <t>金雪宁</t>
+  </si>
+  <si>
     <t>阴明勋</t>
   </si>
   <si>
@@ -85,9 +295,6 @@
     <t>魏成宇</t>
   </si>
   <si>
-    <t>王洁</t>
-  </si>
-  <si>
     <t>孙浩</t>
   </si>
   <si>
@@ -101,9 +308,6 @@
   </si>
   <si>
     <t>管友晶</t>
-  </si>
-  <si>
-    <t>会计</t>
   </si>
   <si>
     <t>杨冬</t>
@@ -344,7 +548,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,11 +560,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -828,133 +1027,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -962,22 +1161,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1291,1354 +1490,991 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="11.6306306306306"/>
+    <col min="2" max="2" width="11.7747747747748" style="1"/>
+    <col min="3" max="3" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>2420100479</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="4">
+        <v>2524100800</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>2420100480</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="4">
+        <v>2524100801</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>2420100481</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="4">
+        <v>2524100802</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
-        <v>2420100482</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="4">
+        <v>2524100803</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>2420100483</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2524100804</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>2420100484</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="4">
+        <v>2524100805</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>2420100485</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="4">
+        <v>2524100806</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
-        <v>2420100486</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="4">
+        <v>2524100807</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
-        <v>2420100487</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="4">
+        <v>2524100808</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>2420100488</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="4">
+        <v>2524100809</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>2420100489</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="4">
+        <v>2524100810</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
-        <v>2420100490</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="4">
+        <v>2524100811</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
-        <v>2420100491</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="4">
+        <v>2524100812</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
-        <v>2420100492</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="B15" s="4">
+        <v>2524100813</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
-        <v>2420100493</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="4">
+        <v>2524100814</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
-        <v>2420100494</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="4">
+        <v>2524100815</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
-        <v>2423100628</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="4">
+        <v>2524100816</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
-        <v>2423100629</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="B19" s="4">
+        <v>2524100817</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>2321100136</v>
-      </c>
-      <c r="C20" s="3" t="s">
+        <v>2524100818</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>24</v>
+      <c r="D20" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>2421100032</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="3" t="s">
+        <v>2524100819</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4">
-        <v>2421100036</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>24</v>
+        <v>2524100820</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>2421100037</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>24</v>
+        <v>2524100821</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>2421100038</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>24</v>
+        <v>2524100822</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>2421100901</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>24</v>
+        <v>2524100823</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>2424100690</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>24</v>
+        <v>2524100824</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="3">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>2424100691</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>2524100825</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>2424100692</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>2524100827</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>2424100693</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
+        <v>2524100828</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>2424100694</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>24</v>
+        <v>2524100829</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>2424100695</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>24</v>
+        <v>2524100830</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4">
-        <v>2424100696</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>24</v>
+        <v>2524100831</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4">
-        <v>2424100697</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>24</v>
+        <v>2524100832</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4">
-        <v>2424100698</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>24</v>
+        <v>2524100833</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>2424100699</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>24</v>
+        <v>2524100834</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4">
-        <v>2424100700</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>24</v>
+        <v>2524100835</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>2421100701</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>24</v>
+        <v>2524100836</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B38" s="4">
-        <v>2424100702</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>24</v>
+        <v>2524100837</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>2421100703</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>24</v>
+        <v>2524100838</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B40" s="4">
-        <v>2421100704</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>24</v>
+        <v>2524100839</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B41" s="4">
-        <v>2424100705</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>24</v>
+        <v>2524100840</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="3">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B42" s="4">
-        <v>2424100706</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>24</v>
+        <v>2524100841</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B43" s="4">
-        <v>2424100707</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>24</v>
+        <v>2524100842</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B44" s="4">
-        <v>2424100708</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>24</v>
+        <v>2524100843</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B45" s="4">
-        <v>2424100709</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>24</v>
+        <v>2524100844</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B46" s="4">
-        <v>2424100710</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>24</v>
+        <v>2524100845</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="3">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4">
-        <v>2424100711</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>24</v>
+        <v>2524100846</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="3">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B48" s="4">
-        <v>2421100712</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>24</v>
+        <v>2524100847</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="3">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4">
-        <v>2421100713</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>24</v>
+        <v>2524100848</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="3">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B50" s="4">
-        <v>2421100714</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>24</v>
+        <v>2524100849</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="3">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B51" s="4">
-        <v>2424100715</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>24</v>
+        <v>2524100850</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="3">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B52" s="4">
-        <v>2424100716</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>24</v>
+        <v>2524100851</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B53" s="4">
-        <v>2424100717</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>24</v>
+        <v>2524100852</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="3">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B54" s="4">
-        <v>2424100718</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>24</v>
+        <v>2524100853</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4">
-        <v>2424100719</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>24</v>
+        <v>2524100854</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="3">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B56" s="4">
-        <v>2424100720</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>24</v>
+        <v>2524100855</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="3">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4">
-        <v>2424100721</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>24</v>
+        <v>2524100856</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="3">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B58" s="4">
-        <v>2421100722</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>24</v>
+        <v>2524100857</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="3">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4">
-        <v>2424100723</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>24</v>
+        <v>2524100858</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="3">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4">
-        <v>2424100724</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>24</v>
+        <v>2524100859</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="3">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B61" s="4">
-        <v>2424100725</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>24</v>
+        <v>2524100860</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="3">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B62" s="4">
-        <v>2424100726</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>24</v>
+        <v>2524100861</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="3">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B63" s="4">
-        <v>2424100727</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>24</v>
+        <v>2524100862</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="3">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4">
-        <v>2424100728</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>24</v>
+        <v>2524100863</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="3">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B65" s="4">
-        <v>2424100729</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>24</v>
+        <v>2524100864</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="3">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4">
-        <v>2421100730</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>24</v>
+        <v>2524100865</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="3">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B67" s="4">
-        <v>2421100731</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>24</v>
+        <v>2524100866</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="3">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B68" s="4">
-        <v>2421100732</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>24</v>
+        <v>2524100867</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="3">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B69" s="4">
-        <v>2421100733</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>24</v>
+        <v>2524100868</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="3">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B70" s="4">
-        <v>2424100734</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="3">
-        <v>52</v>
-      </c>
-      <c r="B71" s="4">
-        <v>2424100735</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="3">
-        <v>53</v>
-      </c>
-      <c r="B72" s="4">
-        <v>2421100736</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="3">
-        <v>54</v>
-      </c>
-      <c r="B73" s="4">
-        <v>2424100737</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="3">
-        <v>55</v>
-      </c>
-      <c r="B74" s="4">
-        <v>2424100738</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="3">
-        <v>56</v>
-      </c>
-      <c r="B75" s="4">
-        <v>2421100739</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="3">
-        <v>57</v>
-      </c>
-      <c r="B76" s="4">
-        <v>2421100740</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="3">
-        <v>58</v>
-      </c>
-      <c r="B77" s="4">
-        <v>2424100741</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="3">
-        <v>59</v>
-      </c>
-      <c r="B78" s="4">
-        <v>2421100742</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="3">
-        <v>60</v>
-      </c>
-      <c r="B79" s="4">
-        <v>2424100743</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="3">
-        <v>61</v>
-      </c>
-      <c r="B80" s="4">
-        <v>2421100744</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="3">
-        <v>62</v>
-      </c>
-      <c r="B81" s="4">
-        <v>2421100745</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="3">
-        <v>63</v>
-      </c>
-      <c r="B82" s="4">
-        <v>2421100746</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="3">
-        <v>64</v>
-      </c>
-      <c r="B83" s="4">
-        <v>2421100747</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="3">
-        <v>65</v>
-      </c>
-      <c r="B84" s="4">
-        <v>2424100748</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="3">
-        <v>66</v>
-      </c>
-      <c r="B85" s="4">
-        <v>2424100749</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="3">
-        <v>67</v>
-      </c>
-      <c r="B86" s="4">
-        <v>2421100750</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="3">
-        <v>68</v>
-      </c>
-      <c r="B87" s="4">
-        <v>2424100751</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="3">
-        <v>69</v>
-      </c>
-      <c r="B88" s="4">
-        <v>2424100752</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="3">
-        <v>70</v>
-      </c>
-      <c r="B89" s="4">
-        <v>2421100753</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="3">
-        <v>71</v>
-      </c>
-      <c r="B90" s="4">
-        <v>2424100754</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="3">
-        <v>72</v>
-      </c>
-      <c r="B91" s="4">
-        <v>2421100755</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="3">
+        <v>2524100869</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B92" s="4">
-        <v>2421100756</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="3">
-        <v>74</v>
-      </c>
-      <c r="B93" s="4">
-        <v>2421100757</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="3">
-        <v>75</v>
-      </c>
-      <c r="B94" s="4">
-        <v>2421100758</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="3">
-        <v>76</v>
-      </c>
-      <c r="B95" s="4">
-        <v>2421100759</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="3">
-        <v>77</v>
-      </c>
-      <c r="B96" s="4">
-        <v>2424100760</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>24</v>
+      <c r="D70" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2651,9 +2487,1354 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
-  <sheetData/>
+  <dimension ref="A1:D96"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2420100479</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2420100480</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2420100481</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2420100482</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2420100483</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2420100484</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2420100485</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2420100486</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2420100487</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2420100488</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2420100489</v>
+      </c>
+      <c r="C12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2420100490</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2420100491</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>2420100492</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>2420100493</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>2420100494</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2423100628</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>2423100629</v>
+      </c>
+      <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>2321100136</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>2421100032</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>2421100036</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>2421100037</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>2421100038</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>2421100901</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26">
+        <v>2424100690</v>
+      </c>
+      <c r="C26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>8</v>
+      </c>
+      <c r="B27">
+        <v>2424100691</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>9</v>
+      </c>
+      <c r="B28">
+        <v>2424100692</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>10</v>
+      </c>
+      <c r="B29">
+        <v>2424100693</v>
+      </c>
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>2424100694</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>12</v>
+      </c>
+      <c r="B31">
+        <v>2424100695</v>
+      </c>
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>13</v>
+      </c>
+      <c r="B32">
+        <v>2424100696</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>14</v>
+      </c>
+      <c r="B33">
+        <v>2424100697</v>
+      </c>
+      <c r="C33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
+        <v>15</v>
+      </c>
+      <c r="B34">
+        <v>2424100698</v>
+      </c>
+      <c r="C34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>16</v>
+      </c>
+      <c r="B35">
+        <v>2424100699</v>
+      </c>
+      <c r="C35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>17</v>
+      </c>
+      <c r="B36">
+        <v>2424100700</v>
+      </c>
+      <c r="C36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>18</v>
+      </c>
+      <c r="B37">
+        <v>2421100701</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>19</v>
+      </c>
+      <c r="B38">
+        <v>2424100702</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>20</v>
+      </c>
+      <c r="B39">
+        <v>2421100703</v>
+      </c>
+      <c r="C39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>21</v>
+      </c>
+      <c r="B40">
+        <v>2421100704</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
+        <v>22</v>
+      </c>
+      <c r="B41">
+        <v>2424100705</v>
+      </c>
+      <c r="C41" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>23</v>
+      </c>
+      <c r="B42">
+        <v>2424100706</v>
+      </c>
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>24</v>
+      </c>
+      <c r="B43">
+        <v>2424100707</v>
+      </c>
+      <c r="C43" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>25</v>
+      </c>
+      <c r="B44">
+        <v>2424100708</v>
+      </c>
+      <c r="C44" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45">
+        <v>26</v>
+      </c>
+      <c r="B45">
+        <v>2424100709</v>
+      </c>
+      <c r="C45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46">
+        <v>27</v>
+      </c>
+      <c r="B46">
+        <v>2424100710</v>
+      </c>
+      <c r="C46" t="s">
+        <v>118</v>
+      </c>
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>28</v>
+      </c>
+      <c r="B47">
+        <v>2424100711</v>
+      </c>
+      <c r="C47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>29</v>
+      </c>
+      <c r="B48">
+        <v>2421100712</v>
+      </c>
+      <c r="C48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>30</v>
+      </c>
+      <c r="B49">
+        <v>2421100713</v>
+      </c>
+      <c r="C49" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>31</v>
+      </c>
+      <c r="B50">
+        <v>2421100714</v>
+      </c>
+      <c r="C50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>32</v>
+      </c>
+      <c r="B51">
+        <v>2424100715</v>
+      </c>
+      <c r="C51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>33</v>
+      </c>
+      <c r="B52">
+        <v>2424100716</v>
+      </c>
+      <c r="C52" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>34</v>
+      </c>
+      <c r="B53">
+        <v>2424100717</v>
+      </c>
+      <c r="C53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>35</v>
+      </c>
+      <c r="B54">
+        <v>2424100718</v>
+      </c>
+      <c r="C54" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>36</v>
+      </c>
+      <c r="B55">
+        <v>2424100719</v>
+      </c>
+      <c r="C55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>37</v>
+      </c>
+      <c r="B56">
+        <v>2424100720</v>
+      </c>
+      <c r="C56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>38</v>
+      </c>
+      <c r="B57">
+        <v>2424100721</v>
+      </c>
+      <c r="C57" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>39</v>
+      </c>
+      <c r="B58">
+        <v>2421100722</v>
+      </c>
+      <c r="C58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>40</v>
+      </c>
+      <c r="B59">
+        <v>2424100723</v>
+      </c>
+      <c r="C59" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>41</v>
+      </c>
+      <c r="B60">
+        <v>2424100724</v>
+      </c>
+      <c r="C60" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>42</v>
+      </c>
+      <c r="B61">
+        <v>2424100725</v>
+      </c>
+      <c r="C61" t="s">
+        <v>133</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62">
+        <v>43</v>
+      </c>
+      <c r="B62">
+        <v>2424100726</v>
+      </c>
+      <c r="C62" t="s">
+        <v>134</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63">
+        <v>44</v>
+      </c>
+      <c r="B63">
+        <v>2424100727</v>
+      </c>
+      <c r="C63" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64">
+        <v>45</v>
+      </c>
+      <c r="B64">
+        <v>2424100728</v>
+      </c>
+      <c r="C64" t="s">
+        <v>136</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65">
+        <v>46</v>
+      </c>
+      <c r="B65">
+        <v>2424100729</v>
+      </c>
+      <c r="C65" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66">
+        <v>47</v>
+      </c>
+      <c r="B66">
+        <v>2421100730</v>
+      </c>
+      <c r="C66" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67">
+        <v>48</v>
+      </c>
+      <c r="B67">
+        <v>2421100731</v>
+      </c>
+      <c r="C67" t="s">
+        <v>139</v>
+      </c>
+      <c r="D67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68">
+        <v>49</v>
+      </c>
+      <c r="B68">
+        <v>2421100732</v>
+      </c>
+      <c r="C68" t="s">
+        <v>140</v>
+      </c>
+      <c r="D68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69">
+        <v>50</v>
+      </c>
+      <c r="B69">
+        <v>2421100733</v>
+      </c>
+      <c r="C69" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70">
+        <v>51</v>
+      </c>
+      <c r="B70">
+        <v>2424100734</v>
+      </c>
+      <c r="C70" t="s">
+        <v>142</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71">
+        <v>52</v>
+      </c>
+      <c r="B71">
+        <v>2424100735</v>
+      </c>
+      <c r="C71" t="s">
+        <v>143</v>
+      </c>
+      <c r="D71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72">
+        <v>53</v>
+      </c>
+      <c r="B72">
+        <v>2421100736</v>
+      </c>
+      <c r="C72" t="s">
+        <v>144</v>
+      </c>
+      <c r="D72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73">
+        <v>54</v>
+      </c>
+      <c r="B73">
+        <v>2424100737</v>
+      </c>
+      <c r="C73" t="s">
+        <v>145</v>
+      </c>
+      <c r="D73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74">
+        <v>55</v>
+      </c>
+      <c r="B74">
+        <v>2424100738</v>
+      </c>
+      <c r="C74" t="s">
+        <v>146</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75">
+        <v>56</v>
+      </c>
+      <c r="B75">
+        <v>2421100739</v>
+      </c>
+      <c r="C75" t="s">
+        <v>147</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76">
+        <v>57</v>
+      </c>
+      <c r="B76">
+        <v>2421100740</v>
+      </c>
+      <c r="C76" t="s">
+        <v>148</v>
+      </c>
+      <c r="D76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77">
+        <v>58</v>
+      </c>
+      <c r="B77">
+        <v>2424100741</v>
+      </c>
+      <c r="C77" t="s">
+        <v>149</v>
+      </c>
+      <c r="D77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78">
+        <v>59</v>
+      </c>
+      <c r="B78">
+        <v>2421100742</v>
+      </c>
+      <c r="C78" t="s">
+        <v>150</v>
+      </c>
+      <c r="D78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79">
+        <v>60</v>
+      </c>
+      <c r="B79">
+        <v>2424100743</v>
+      </c>
+      <c r="C79" t="s">
+        <v>151</v>
+      </c>
+      <c r="D79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80">
+        <v>61</v>
+      </c>
+      <c r="B80">
+        <v>2421100744</v>
+      </c>
+      <c r="C80" t="s">
+        <v>152</v>
+      </c>
+      <c r="D80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81">
+        <v>62</v>
+      </c>
+      <c r="B81">
+        <v>2421100745</v>
+      </c>
+      <c r="C81" t="s">
+        <v>153</v>
+      </c>
+      <c r="D81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82">
+        <v>63</v>
+      </c>
+      <c r="B82">
+        <v>2421100746</v>
+      </c>
+      <c r="C82" t="s">
+        <v>154</v>
+      </c>
+      <c r="D82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83">
+        <v>64</v>
+      </c>
+      <c r="B83">
+        <v>2421100747</v>
+      </c>
+      <c r="C83" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84">
+        <v>65</v>
+      </c>
+      <c r="B84">
+        <v>2424100748</v>
+      </c>
+      <c r="C84" t="s">
+        <v>156</v>
+      </c>
+      <c r="D84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85">
+        <v>66</v>
+      </c>
+      <c r="B85">
+        <v>2424100749</v>
+      </c>
+      <c r="C85" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86">
+        <v>67</v>
+      </c>
+      <c r="B86">
+        <v>2421100750</v>
+      </c>
+      <c r="C86" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87">
+        <v>68</v>
+      </c>
+      <c r="B87">
+        <v>2424100751</v>
+      </c>
+      <c r="C87" t="s">
+        <v>159</v>
+      </c>
+      <c r="D87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88">
+        <v>69</v>
+      </c>
+      <c r="B88">
+        <v>2424100752</v>
+      </c>
+      <c r="C88" t="s">
+        <v>160</v>
+      </c>
+      <c r="D88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89">
+        <v>70</v>
+      </c>
+      <c r="B89">
+        <v>2421100753</v>
+      </c>
+      <c r="C89" t="s">
+        <v>161</v>
+      </c>
+      <c r="D89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90">
+        <v>71</v>
+      </c>
+      <c r="B90">
+        <v>2424100754</v>
+      </c>
+      <c r="C90" t="s">
+        <v>162</v>
+      </c>
+      <c r="D90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91">
+        <v>72</v>
+      </c>
+      <c r="B91">
+        <v>2421100755</v>
+      </c>
+      <c r="C91" t="s">
+        <v>163</v>
+      </c>
+      <c r="D91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92">
+        <v>73</v>
+      </c>
+      <c r="B92">
+        <v>2421100756</v>
+      </c>
+      <c r="C92" t="s">
+        <v>164</v>
+      </c>
+      <c r="D92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93">
+        <v>74</v>
+      </c>
+      <c r="B93">
+        <v>2421100757</v>
+      </c>
+      <c r="C93" t="s">
+        <v>165</v>
+      </c>
+      <c r="D93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94">
+        <v>75</v>
+      </c>
+      <c r="B94">
+        <v>2421100758</v>
+      </c>
+      <c r="C94" t="s">
+        <v>166</v>
+      </c>
+      <c r="D94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95">
+        <v>76</v>
+      </c>
+      <c r="B95">
+        <v>2421100759</v>
+      </c>
+      <c r="C95" t="s">
+        <v>167</v>
+      </c>
+      <c r="D95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96">
+        <v>77</v>
+      </c>
+      <c r="B96">
+        <v>2424100760</v>
+      </c>
+      <c r="C96" t="s">
+        <v>168</v>
+      </c>
+      <c r="D96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
